--- a/ig/main/ValueSet-jdv-j374-autorite.xlsx
+++ b/ig/main/ValueSet-jdv-j374-autorite.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -66,15 +67,12 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-29T09:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -84,9 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs contenant la liste des autorités quelque soit la catégorie d'autorité et quelque soir l'état de l'autorité active ou inactive)</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -99,25 +94,313 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260330120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite</t>
+  </si>
+  <si>
+    <t>ARS-01</t>
+  </si>
+  <si>
+    <t>ARS-01 : Guadeloupe</t>
+  </si>
+  <si>
+    <t>ARS-02</t>
+  </si>
+  <si>
+    <t>ARS-02 : Martinique</t>
+  </si>
+  <si>
+    <t>ARS-03</t>
+  </si>
+  <si>
+    <t>ARS-03 : Guyane</t>
+  </si>
+  <si>
+    <t>ARS-04</t>
+  </si>
+  <si>
+    <t>ARS-04 : Océan Indien (La Réunion et Mayotte)</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite</t>
+    <t>ARS-05</t>
+  </si>
+  <si>
+    <t>ARS-05 : La Réunion</t>
+  </si>
+  <si>
+    <t>ARS-06</t>
+  </si>
+  <si>
+    <t>ARS-06 : Mayotte</t>
+  </si>
+  <si>
+    <t>ARS-11</t>
+  </si>
+  <si>
+    <t>ARS-11 : Ile-de-France</t>
+  </si>
+  <si>
+    <t>ARS-21</t>
+  </si>
+  <si>
+    <t>ARS-21 : Champagne-Ardenne</t>
+  </si>
+  <si>
+    <t>ARS-22</t>
+  </si>
+  <si>
+    <t>ARS-22 : Picardie</t>
+  </si>
+  <si>
+    <t>ARS-23</t>
+  </si>
+  <si>
+    <t>ARS-23 : Haute-Normandie</t>
+  </si>
+  <si>
+    <t>ARS-24</t>
+  </si>
+  <si>
+    <t>ARS-24 : Centre-Val de Loire</t>
+  </si>
+  <si>
+    <t>ARS-25</t>
+  </si>
+  <si>
+    <t>ARS-25 : Basse-Normandie</t>
+  </si>
+  <si>
+    <t>ARS-26</t>
+  </si>
+  <si>
+    <t>ARS-26 : Bourgogne</t>
+  </si>
+  <si>
+    <t>ARS-27</t>
+  </si>
+  <si>
+    <t>ARS-27 : Bourgogne-Franche-Comté</t>
+  </si>
+  <si>
+    <t>ARS-28</t>
+  </si>
+  <si>
+    <t>ARS-28 : Normandie</t>
+  </si>
+  <si>
+    <t>ARS-31</t>
+  </si>
+  <si>
+    <t>ARS-31 : Nord-Pas-de-Calais</t>
+  </si>
+  <si>
+    <t>ARS-32</t>
+  </si>
+  <si>
+    <t>ARS-32 : Hauts-de-France</t>
+  </si>
+  <si>
+    <t>ARS-41</t>
+  </si>
+  <si>
+    <t>ARS-41 : Lorraine</t>
+  </si>
+  <si>
+    <t>ARS-42</t>
+  </si>
+  <si>
+    <t>ARS-42 : Alsace</t>
+  </si>
+  <si>
+    <t>ARS-43</t>
+  </si>
+  <si>
+    <t>ARS-43 : Franche-Comté</t>
+  </si>
+  <si>
+    <t>ARS-44</t>
+  </si>
+  <si>
+    <t>ARS-44 : Grand Est</t>
+  </si>
+  <si>
+    <t>ARS-52</t>
+  </si>
+  <si>
+    <t>ARS-52 : Pays de la Loire</t>
+  </si>
+  <si>
+    <t>ARS-53</t>
+  </si>
+  <si>
+    <t>ARS-53 : Bretagne</t>
+  </si>
+  <si>
+    <t>ARS-54</t>
+  </si>
+  <si>
+    <t>ARS-54 : Poitou-Charentes</t>
+  </si>
+  <si>
+    <t>ARS-72</t>
+  </si>
+  <si>
+    <t>ARS-72 : Aquitaine</t>
+  </si>
+  <si>
+    <t>ARS-73</t>
+  </si>
+  <si>
+    <t>ARS-73 : Midi-Pyrénées</t>
+  </si>
+  <si>
+    <t>ARS-74</t>
+  </si>
+  <si>
+    <t>ARS-74 : Limousin</t>
+  </si>
+  <si>
+    <t>ARS-75</t>
+  </si>
+  <si>
+    <t>ARS-75 : Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>ARS-76</t>
+  </si>
+  <si>
+    <t>ARS-76 : Occitanie</t>
+  </si>
+  <si>
+    <t>ARS-82</t>
+  </si>
+  <si>
+    <t>ARS-82 : Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>ARS-83</t>
+  </si>
+  <si>
+    <t>ARS-83 : Auvergne</t>
+  </si>
+  <si>
+    <t>ARS-84</t>
+  </si>
+  <si>
+    <t>ARS-84 : Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>ARS-91</t>
+  </si>
+  <si>
+    <t>ARS-91 : Languedoc-Roussillon</t>
+  </si>
+  <si>
+    <t>ARS-93</t>
+  </si>
+  <si>
+    <t>ARS-93 : Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>ARS-94</t>
+  </si>
+  <si>
+    <t>ARS-94 : Corse</t>
+  </si>
+  <si>
+    <t>AT-975</t>
+  </si>
+  <si>
+    <t>AT-975 : ATS de Saint-Pierre-Et-Miquelon</t>
+  </si>
+  <si>
+    <t>ENREG</t>
+  </si>
+  <si>
+    <t>Enregistrement par les AE locales (Structures)</t>
+  </si>
+  <si>
+    <t>ONCD</t>
+  </si>
+  <si>
+    <t>Ordre des chirurgiens-dentistes</t>
+  </si>
+  <si>
+    <t>ONI</t>
+  </si>
+  <si>
+    <t>Ordre des infirmiers</t>
+  </si>
+  <si>
+    <t>CNOMK</t>
+  </si>
+  <si>
+    <t>Ordre des masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>CNOM</t>
+  </si>
+  <si>
+    <t>Ordre des médecins</t>
+  </si>
+  <si>
+    <t>CNOP</t>
+  </si>
+  <si>
+    <t>Ordre des pharmaciens</t>
+  </si>
+  <si>
+    <t>CNOPP</t>
+  </si>
+  <si>
+    <t>Ordre des pédicures-podologues</t>
+  </si>
+  <si>
+    <t>CNOSF</t>
+  </si>
+  <si>
+    <t>Ordre des sages-femmes</t>
+  </si>
+  <si>
+    <t>SSA</t>
+  </si>
+  <si>
+    <t>Service de santé des armées</t>
   </si>
 </sst>
 </file>
@@ -334,44 +617,40 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -381,49 +660,1009 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>32</v>
       </c>
+      <c r="E1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j374-autorite.xlsx
+++ b/ig/main/ValueSet-jdv-j374-autorite.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -118,6 +120,309 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260330120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ARS-01</t>
+  </si>
+  <si>
+    <t>ARS-01 : Guadeloupe</t>
+  </si>
+  <si>
+    <t>ARS-02</t>
+  </si>
+  <si>
+    <t>ARS-02 : Martinique</t>
+  </si>
+  <si>
+    <t>ARS-03</t>
+  </si>
+  <si>
+    <t>ARS-03 : Guyane</t>
+  </si>
+  <si>
+    <t>ARS-04</t>
+  </si>
+  <si>
+    <t>ARS-04 : Océan Indien (La Réunion et Mayotte)</t>
+  </si>
+  <si>
+    <t>ARS-05</t>
+  </si>
+  <si>
+    <t>ARS-05 : La Réunion</t>
+  </si>
+  <si>
+    <t>ARS-06</t>
+  </si>
+  <si>
+    <t>ARS-06 : Mayotte</t>
+  </si>
+  <si>
+    <t>ARS-11</t>
+  </si>
+  <si>
+    <t>ARS-11 : Ile-de-France</t>
+  </si>
+  <si>
+    <t>ARS-21</t>
+  </si>
+  <si>
+    <t>ARS-21 : Champagne-Ardenne</t>
+  </si>
+  <si>
+    <t>ARS-22</t>
+  </si>
+  <si>
+    <t>ARS-22 : Picardie</t>
+  </si>
+  <si>
+    <t>ARS-23</t>
+  </si>
+  <si>
+    <t>ARS-23 : Haute-Normandie</t>
+  </si>
+  <si>
+    <t>ARS-24</t>
+  </si>
+  <si>
+    <t>ARS-24 : Centre-Val de Loire</t>
+  </si>
+  <si>
+    <t>ARS-25</t>
+  </si>
+  <si>
+    <t>ARS-25 : Basse-Normandie</t>
+  </si>
+  <si>
+    <t>ARS-26</t>
+  </si>
+  <si>
+    <t>ARS-26 : Bourgogne</t>
+  </si>
+  <si>
+    <t>ARS-27</t>
+  </si>
+  <si>
+    <t>ARS-27 : Bourgogne-Franche-Comté</t>
+  </si>
+  <si>
+    <t>ARS-28</t>
+  </si>
+  <si>
+    <t>ARS-28 : Normandie</t>
+  </si>
+  <si>
+    <t>ARS-31</t>
+  </si>
+  <si>
+    <t>ARS-31 : Nord-Pas-de-Calais</t>
+  </si>
+  <si>
+    <t>ARS-32</t>
+  </si>
+  <si>
+    <t>ARS-32 : Hauts-de-France</t>
+  </si>
+  <si>
+    <t>ARS-41</t>
+  </si>
+  <si>
+    <t>ARS-41 : Lorraine</t>
+  </si>
+  <si>
+    <t>ARS-42</t>
+  </si>
+  <si>
+    <t>ARS-42 : Alsace</t>
+  </si>
+  <si>
+    <t>ARS-43</t>
+  </si>
+  <si>
+    <t>ARS-43 : Franche-Comté</t>
+  </si>
+  <si>
+    <t>ARS-44</t>
+  </si>
+  <si>
+    <t>ARS-44 : Grand Est</t>
+  </si>
+  <si>
+    <t>ARS-52</t>
+  </si>
+  <si>
+    <t>ARS-52 : Pays de la Loire</t>
+  </si>
+  <si>
+    <t>ARS-53</t>
+  </si>
+  <si>
+    <t>ARS-53 : Bretagne</t>
+  </si>
+  <si>
+    <t>ARS-54</t>
+  </si>
+  <si>
+    <t>ARS-54 : Poitou-Charentes</t>
+  </si>
+  <si>
+    <t>ARS-72</t>
+  </si>
+  <si>
+    <t>ARS-72 : Aquitaine</t>
+  </si>
+  <si>
+    <t>ARS-73</t>
+  </si>
+  <si>
+    <t>ARS-73 : Midi-Pyrénées</t>
+  </si>
+  <si>
+    <t>ARS-74</t>
+  </si>
+  <si>
+    <t>ARS-74 : Limousin</t>
+  </si>
+  <si>
+    <t>ARS-75</t>
+  </si>
+  <si>
+    <t>ARS-75 : Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>ARS-76</t>
+  </si>
+  <si>
+    <t>ARS-76 : Occitanie</t>
+  </si>
+  <si>
+    <t>ARS-82</t>
+  </si>
+  <si>
+    <t>ARS-82 : Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>ARS-83</t>
+  </si>
+  <si>
+    <t>ARS-83 : Auvergne</t>
+  </si>
+  <si>
+    <t>ARS-84</t>
+  </si>
+  <si>
+    <t>ARS-84 : Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>ARS-91</t>
+  </si>
+  <si>
+    <t>ARS-91 : Languedoc-Roussillon</t>
+  </si>
+  <si>
+    <t>ARS-93</t>
+  </si>
+  <si>
+    <t>ARS-93 : Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>ARS-94</t>
+  </si>
+  <si>
+    <t>ARS-94 : Corse</t>
+  </si>
+  <si>
+    <t>AT-975</t>
+  </si>
+  <si>
+    <t>AT-975 : ATS de Saint-Pierre-Et-Miquelon</t>
+  </si>
+  <si>
+    <t>ENREG</t>
+  </si>
+  <si>
+    <t>Enregistrement par les AE locales (Structures)</t>
+  </si>
+  <si>
+    <t>ONCD</t>
+  </si>
+  <si>
+    <t>Ordre des chirurgiens-dentistes</t>
+  </si>
+  <si>
+    <t>ONI</t>
+  </si>
+  <si>
+    <t>Ordre des infirmiers</t>
+  </si>
+  <si>
+    <t>CNOMK</t>
+  </si>
+  <si>
+    <t>Ordre des masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>CNOM</t>
+  </si>
+  <si>
+    <t>Ordre des médecins</t>
+  </si>
+  <si>
+    <t>CNOP</t>
+  </si>
+  <si>
+    <t>Ordre des pharmaciens</t>
+  </si>
+  <si>
+    <t>CNOPP</t>
+  </si>
+  <si>
+    <t>Ordre des pédicures-podologues</t>
+  </si>
+  <si>
+    <t>CNOSF</t>
+  </si>
+  <si>
+    <t>Ordre des sages-femmes</t>
+  </si>
+  <si>
+    <t>SSA</t>
+  </si>
+  <si>
+    <t>Service de santé des armées</t>
   </si>
 </sst>
 </file>
@@ -429,4 +734,1016 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/main/ValueSet-jdv-j374-autorite.xlsx
+++ b/ig/main/ValueSet-jdv-j374-autorite.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="198">
   <si>
     <t>Property</t>
   </si>
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260330120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r396-autorite|20260629120000</t>
   </si>
   <si>
     <t>version</t>
@@ -369,6 +369,192 @@
   </si>
   <si>
     <t>AT-975 : ATS de Saint-Pierre-Et-Miquelon</t>
+  </si>
+  <si>
+    <t>CD-01</t>
+  </si>
+  <si>
+    <t>CD-01 : Conseil départemental de l'Ain</t>
+  </si>
+  <si>
+    <t>CD-02</t>
+  </si>
+  <si>
+    <t>CD-02 : Conseil départemental del'Aisne</t>
+  </si>
+  <si>
+    <t>CD-03</t>
+  </si>
+  <si>
+    <t>CD-03 : Conseil départemental de l'Allier</t>
+  </si>
+  <si>
+    <t>CD-15</t>
+  </si>
+  <si>
+    <t>CD-15 : Conseil départemental du Cantal</t>
+  </si>
+  <si>
+    <t>CD-54</t>
+  </si>
+  <si>
+    <t>CD-54 : Conseil départemental de Meurthe et Moselle</t>
+  </si>
+  <si>
+    <t>CD-58</t>
+  </si>
+  <si>
+    <t>CD-58 : Conseil départemental de la Nièvre</t>
+  </si>
+  <si>
+    <t>CD-94</t>
+  </si>
+  <si>
+    <t>CD-94 : Conseil départemental du Val de Marne</t>
+  </si>
+  <si>
+    <t>CD-95</t>
+  </si>
+  <si>
+    <t>CD-95 : Conseil départemental du Val d'Oise</t>
+  </si>
+  <si>
+    <t>DDETS-01</t>
+  </si>
+  <si>
+    <t>DDETS-01 : Direction départementale de l'emploi, du travail et des solidarités Ain</t>
+  </si>
+  <si>
+    <t>DDETS-02</t>
+  </si>
+  <si>
+    <t>DDETS-02 : Direction départementale de l'emploi, du travail et des solidarités Aisne</t>
+  </si>
+  <si>
+    <t>DDETS-03</t>
+  </si>
+  <si>
+    <t>DDETS-03 : Direction départementale de l'emploi, du travail et des solidarités Allier</t>
+  </si>
+  <si>
+    <t>DDETS-95</t>
+  </si>
+  <si>
+    <t>DDETS-95 :Direction départementale de l'emploi, du travail et des solidarités Val d'Oise</t>
+  </si>
+  <si>
+    <t>DREETS-01</t>
+  </si>
+  <si>
+    <t>DREETS-01 : Direction de l'économie de l'emploi du travail et des solidarités Guadeloupe</t>
+  </si>
+  <si>
+    <t>DREETS-02</t>
+  </si>
+  <si>
+    <t>DREETS-02 :  Direction de l'économie de l'emploi du travail et des solidarités Martinique</t>
+  </si>
+  <si>
+    <t>DREETS-03</t>
+  </si>
+  <si>
+    <t>DREETS-03 :  Direction générale cohésion et population Guyane</t>
+  </si>
+  <si>
+    <t>DREETS-05</t>
+  </si>
+  <si>
+    <t>DREETS-05 :  Direction de l'économie de l'emploi du travail et des solidarités de La Réunion</t>
+  </si>
+  <si>
+    <t>DREETS-06</t>
+  </si>
+  <si>
+    <t>DREETS-06 : Direction de l'économie de l'emploi du travail et des solidarités Mayotte</t>
+  </si>
+  <si>
+    <t>DREETS-11</t>
+  </si>
+  <si>
+    <t>DREETS-11 : Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités d'Ile de France</t>
+  </si>
+  <si>
+    <t>DREETS-24</t>
+  </si>
+  <si>
+    <t>DREETS-24 :  Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Centre-Val de Loire</t>
+  </si>
+  <si>
+    <t>DREETS-27</t>
+  </si>
+  <si>
+    <t>DREETS-27 :  Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Bourgogne-Franche-Comté</t>
+  </si>
+  <si>
+    <t>DREETS-28</t>
+  </si>
+  <si>
+    <t>DREETS-28 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Normandie</t>
+  </si>
+  <si>
+    <t>DREETS-32</t>
+  </si>
+  <si>
+    <t>DREETS-32 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Hauts-de-France</t>
+  </si>
+  <si>
+    <t>DREETS-44</t>
+  </si>
+  <si>
+    <t>DREETS-44 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Grand Est</t>
+  </si>
+  <si>
+    <t>DREETS-52</t>
+  </si>
+  <si>
+    <t>DREETS-52 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Pays de la Loire</t>
+  </si>
+  <si>
+    <t>DREETS-53</t>
+  </si>
+  <si>
+    <t>DREETS-53 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Bretagne</t>
+  </si>
+  <si>
+    <t>DREETS-75</t>
+  </si>
+  <si>
+    <t>DREETS-75 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>DREETS-76</t>
+  </si>
+  <si>
+    <t>DREETS-76 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Occitanie</t>
+  </si>
+  <si>
+    <t>DREETS-84</t>
+  </si>
+  <si>
+    <t>DREETS-84 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>DREETS-93</t>
+  </si>
+  <si>
+    <t>DREETS-93 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>DREETS-94</t>
+  </si>
+  <si>
+    <t>DREETS-94 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités de Corse</t>
+  </si>
+  <si>
+    <t>DRHIL-11</t>
+  </si>
+  <si>
+    <t>DRHIL-11 : Direction régionale et interdépartementale de l'Hébergement et du Logement Ile de France</t>
   </si>
   <si>
     <t>ENREG</t>
@@ -772,7 +958,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1743,6 +1929,657 @@
         <v>15</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
